--- a/reports/20260506/UI_BLOCK_UNBLOCK_FEEDBACK_STANDALONE_INT_PW.xlsx
+++ b/reports/20260506/UI_BLOCK_UNBLOCK_FEEDBACK_STANDALONE_INT_PW.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11:38:55</t>
+          <t>18:26:11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11:39:03</t>
+          <t>18:26:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -553,14 +553,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>62.59s</t>
+          <t>32.21s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11:39:06</t>
+          <t>18:26:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -582,7 +582,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11:39:06</t>
+          <t>18:26:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -604,7 +604,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11:39:07</t>
+          <t>18:26:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11:39:08</t>
+          <t>18:26:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11:39:20</t>
+          <t>18:26:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -670,7 +670,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11:39:20</t>
+          <t>18:26:23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11:39:20</t>
+          <t>18:26:23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11:39:20</t>
+          <t>18:26:23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -736,7 +736,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11:39:21</t>
+          <t>18:26:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11:39:21</t>
+          <t>18:26:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11:39:24</t>
+          <t>18:26:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11:39:24</t>
+          <t>18:26:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11:39:25</t>
+          <t>18:26:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11:39:25</t>
+          <t>18:26:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -868,7 +868,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11:39:32</t>
+          <t>18:26:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11:39:33</t>
+          <t>18:26:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11:39:41</t>
+          <t>18:26:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11:39:41</t>
+          <t>18:26:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11:39:41</t>
+          <t>18:26:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11:39:41</t>
+          <t>18:26:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1000,7 +1000,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11:39:41</t>
+          <t>18:26:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1022,7 +1022,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11:39:41</t>
+          <t>18:26:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1044,7 +1044,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11:39:42</t>
+          <t>18:26:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11:39:42</t>
+          <t>18:26:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11:39:44</t>
+          <t>18:26:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1110,7 +1110,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11:39:44</t>
+          <t>18:26:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11:39:44</t>
+          <t>18:26:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1154,7 +1154,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11:39:44</t>
+          <t>18:26:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11:39:44</t>
+          <t>18:26:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11:39:47</t>
+          <t>18:26:37</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11:39:54</t>
+          <t>18:26:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11:39:56</t>
+          <t>18:26:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11:39:56</t>
+          <t>18:26:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
